--- a/서버정보/20260911_리소스배포_운영.xlsx
+++ b/서버정보/20260911_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F100F2-1406-4DBB-8D38-2213E8B5C2B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CC1701-44BB-42BA-A4DD-F198171B1669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7932" uniqueCount="1158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7920" uniqueCount="1157">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5729,10 +5729,6 @@
   </si>
   <si>
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.8_Base_Image/versions/0.0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TURE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -6475,7 +6471,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6851,19 +6847,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -13135,10 +13119,10 @@
         <v>SEC</v>
       </c>
       <c r="D67" s="74" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E67" s="74" t="s">
         <v>1110</v>
-      </c>
-      <c r="E67" s="74" t="s">
-        <v>1111</v>
       </c>
       <c r="F67" s="74" t="str">
         <f t="shared" ref="F67" si="26">SUBSTITUTE(E67, "hazr-", "")&amp;"-rule"&amp;O67</f>
@@ -13196,10 +13180,10 @@
         <v>SEC</v>
       </c>
       <c r="D68" s="74" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E68" s="74" t="s">
         <v>1110</v>
-      </c>
-      <c r="E68" s="74" t="s">
-        <v>1111</v>
       </c>
       <c r="F68" s="74" t="str">
         <f t="shared" ref="F68:F72" si="30">SUBSTITUTE(E68, "hazr-", "")&amp;"-rule"&amp;O68</f>
@@ -13257,10 +13241,10 @@
         <v>SEC</v>
       </c>
       <c r="D69" s="74" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E69" s="74" t="s">
         <v>1110</v>
-      </c>
-      <c r="E69" s="74" t="s">
-        <v>1111</v>
       </c>
       <c r="F69" s="74" t="str">
         <f t="shared" si="30"/>
@@ -13318,10 +13302,10 @@
         <v>SEC</v>
       </c>
       <c r="D70" s="74" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E70" s="74" t="s">
         <v>1110</v>
-      </c>
-      <c r="E70" s="74" t="s">
-        <v>1111</v>
       </c>
       <c r="F70" s="74" t="str">
         <f t="shared" si="30"/>
@@ -13379,10 +13363,10 @@
         <v>SEC</v>
       </c>
       <c r="D71" s="74" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E71" s="74" t="s">
         <v>1110</v>
-      </c>
-      <c r="E71" s="74" t="s">
-        <v>1111</v>
       </c>
       <c r="F71" s="74" t="str">
         <f t="shared" si="30"/>
@@ -13440,10 +13424,10 @@
         <v>SEC</v>
       </c>
       <c r="D72" s="74" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E72" s="74" t="s">
         <v>1110</v>
-      </c>
-      <c r="E72" s="74" t="s">
-        <v>1111</v>
       </c>
       <c r="F72" s="74" t="str">
         <f t="shared" si="30"/>
@@ -13501,10 +13485,10 @@
         <v>DIS</v>
       </c>
       <c r="D73" s="125" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E73" s="82" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="F73" s="74" t="str">
         <f t="shared" ref="F73:F77" si="34">SUBSTITUTE(E73, "hazr-", "")&amp;"-rule"&amp;O73</f>
@@ -13562,10 +13546,10 @@
         <v>DIS</v>
       </c>
       <c r="D74" s="125" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E74" s="74" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="F74" s="74" t="str">
         <f t="shared" si="34"/>
@@ -13623,10 +13607,10 @@
         <v>DIS</v>
       </c>
       <c r="D75" s="125" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E75" s="82" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="F75" s="74" t="str">
         <f t="shared" si="34"/>
@@ -13684,10 +13668,10 @@
         <v>DIS</v>
       </c>
       <c r="D76" s="125" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E76" s="74" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F76" s="74" t="str">
         <f t="shared" si="34"/>
@@ -13745,10 +13729,10 @@
         <v>DIS</v>
       </c>
       <c r="D77" s="125" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E77" s="82" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="F77" s="74" t="str">
         <f t="shared" si="34"/>
@@ -26933,7 +26917,7 @@
         <v>317</v>
       </c>
       <c r="Y145" s="95" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="Z145" s="95" t="s">
         <v>965</v>
@@ -27022,10 +27006,10 @@
         <v>317</v>
       </c>
       <c r="Y146" s="95" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="Z146" s="95" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="AA146" s="95" t="b">
         <v>1</v>
@@ -27101,20 +27085,20 @@
         <f>SUBSTITUTE(F147,"hazr-","")&amp;"-nic"</f>
         <v>p-sec-mevrsol02-nic</v>
       </c>
-      <c r="V147" s="95" t="s">
+      <c r="V147" s="95" t="b">
+        <v>1</v>
+      </c>
+      <c r="W147" s="95" t="b">
+        <v>1</v>
+      </c>
+      <c r="X147" s="95" t="s">
+        <v>317</v>
+      </c>
+      <c r="Y147" s="95" t="s">
         <v>1106</v>
       </c>
-      <c r="W147" s="95" t="s">
-        <v>1106</v>
-      </c>
-      <c r="X147" s="95" t="s">
-        <v>317</v>
-      </c>
-      <c r="Y147" s="95" t="s">
-        <v>1107</v>
-      </c>
       <c r="Z147" s="95" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="AA147" s="95" t="b">
         <v>1</v>
@@ -27135,24 +27119,24 @@
       <c r="B148" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C148" s="126" t="str" cm="1">
+      <c r="C148" s="74" t="str" cm="1">
         <f t="array" ref="C148">UPPER(INDEX(_xlfn.TEXTSPLIT($F148, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D148" s="126" t="s">
-        <v>1117</v>
+      <c r="D148" s="74" t="s">
+        <v>1116</v>
       </c>
       <c r="E148" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F148" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G148" s="74" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="H148" s="74" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="I148" s="74">
         <v>4</v>
@@ -27172,7 +27156,7 @@
       <c r="N148" s="124" t="s">
         <v>1102</v>
       </c>
-      <c r="O148" s="127" t="str">
+      <c r="O148" s="120" t="str">
         <f t="shared" ref="O148:O157" si="18">SUBSTITUTE(F148,"hazr-","")&amp;"-osdisk"</f>
         <v>p-dis-clvweb01-osdisk</v>
       </c>
@@ -27182,10 +27166,10 @@
       <c r="Q148" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R148" s="126"/>
+      <c r="R148" s="74"/>
       <c r="S148" s="74"/>
-      <c r="T148" s="126"/>
-      <c r="U148" s="126" t="str">
+      <c r="T148" s="74"/>
+      <c r="U148" s="74" t="str">
         <f t="shared" ref="U148:U157" si="19">SUBSTITUTE(F148,"hazr-","")&amp;"-nic"</f>
         <v>p-dis-clvweb01-nic</v>
       </c>
@@ -27223,24 +27207,24 @@
       <c r="B149" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C149" s="126" t="str" cm="1">
+      <c r="C149" s="74" t="str" cm="1">
         <f t="array" ref="C149">UPPER(INDEX(_xlfn.TEXTSPLIT($F149, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D149" s="126" t="s">
-        <v>1117</v>
+      <c r="D149" s="74" t="s">
+        <v>1116</v>
       </c>
       <c r="E149" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F149" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G149" s="74" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="H149" s="74" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="I149" s="74">
         <v>4</v>
@@ -27260,7 +27244,7 @@
       <c r="N149" s="124" t="s">
         <v>1102</v>
       </c>
-      <c r="O149" s="127" t="str">
+      <c r="O149" s="120" t="str">
         <f t="shared" si="18"/>
         <v>p-dis-clvweb02-osdisk</v>
       </c>
@@ -27270,18 +27254,18 @@
       <c r="Q149" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R149" s="126"/>
+      <c r="R149" s="74"/>
       <c r="S149" s="74"/>
-      <c r="T149" s="126"/>
-      <c r="U149" s="126" t="str">
+      <c r="T149" s="74"/>
+      <c r="U149" s="74" t="str">
         <f t="shared" si="19"/>
         <v>p-dis-clvweb02-nic</v>
       </c>
-      <c r="V149" s="95" t="s">
-        <v>1106</v>
-      </c>
-      <c r="W149" s="95" t="s">
-        <v>1106</v>
+      <c r="V149" s="95" t="b">
+        <v>1</v>
+      </c>
+      <c r="W149" s="95" t="b">
+        <v>1</v>
       </c>
       <c r="X149" s="95" t="s">
         <v>317</v>
@@ -27311,24 +27295,24 @@
       <c r="B150" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C150" s="126" t="str" cm="1">
+      <c r="C150" s="74" t="str" cm="1">
         <f t="array" ref="C150">UPPER(INDEX(_xlfn.TEXTSPLIT($F150, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D150" s="126" t="s">
-        <v>1117</v>
+      <c r="D150" s="74" t="s">
+        <v>1116</v>
       </c>
       <c r="E150" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F150" s="82" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G150" s="74" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H150" s="74" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="I150" s="74">
         <v>4</v>
@@ -27348,7 +27332,7 @@
       <c r="N150" s="124" t="s">
         <v>1102</v>
       </c>
-      <c r="O150" s="127" t="str">
+      <c r="O150" s="120" t="str">
         <f t="shared" si="18"/>
         <v>p-dis-clvap01-osdisk</v>
       </c>
@@ -27358,10 +27342,10 @@
       <c r="Q150" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R150" s="126"/>
+      <c r="R150" s="74"/>
       <c r="S150" s="74"/>
-      <c r="T150" s="126"/>
-      <c r="U150" s="126" t="str">
+      <c r="T150" s="74"/>
+      <c r="U150" s="74" t="str">
         <f t="shared" si="19"/>
         <v>p-dis-clvap01-nic</v>
       </c>
@@ -27399,24 +27383,24 @@
       <c r="B151" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C151" s="126" t="str" cm="1">
+      <c r="C151" s="74" t="str" cm="1">
         <f t="array" ref="C151">UPPER(INDEX(_xlfn.TEXTSPLIT($F151, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D151" s="126" t="s">
-        <v>1117</v>
+      <c r="D151" s="74" t="s">
+        <v>1116</v>
       </c>
       <c r="E151" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F151" s="74" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G151" s="74" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="H151" s="74" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="I151" s="74">
         <v>4</v>
@@ -27436,7 +27420,7 @@
       <c r="N151" s="124" t="s">
         <v>1102</v>
       </c>
-      <c r="O151" s="127" t="str">
+      <c r="O151" s="120" t="str">
         <f t="shared" si="18"/>
         <v>p-dis-clvap02-osdisk</v>
       </c>
@@ -27446,18 +27430,18 @@
       <c r="Q151" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R151" s="126"/>
+      <c r="R151" s="74"/>
       <c r="S151" s="74"/>
-      <c r="T151" s="126"/>
-      <c r="U151" s="126" t="str">
+      <c r="T151" s="74"/>
+      <c r="U151" s="74" t="str">
         <f t="shared" si="19"/>
         <v>p-dis-clvap02-nic</v>
       </c>
-      <c r="V151" s="95" t="s">
-        <v>1106</v>
-      </c>
-      <c r="W151" s="95" t="s">
-        <v>1106</v>
+      <c r="V151" s="95" t="b">
+        <v>1</v>
+      </c>
+      <c r="W151" s="95" t="b">
+        <v>1</v>
       </c>
       <c r="X151" s="95" t="s">
         <v>317</v>
@@ -27487,24 +27471,24 @@
       <c r="B152" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C152" s="126" t="str" cm="1">
+      <c r="C152" s="74" t="str" cm="1">
         <f t="array" ref="C152">UPPER(INDEX(_xlfn.TEXTSPLIT($F152, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D152" s="126" t="s">
-        <v>1117</v>
+      <c r="D152" s="74" t="s">
+        <v>1116</v>
       </c>
       <c r="E152" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F152" s="82" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G152" s="74" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="H152" s="74" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="I152" s="74">
         <v>4</v>
@@ -27524,7 +27508,7 @@
       <c r="N152" s="124" t="s">
         <v>1102</v>
       </c>
-      <c r="O152" s="127" t="str">
+      <c r="O152" s="120" t="str">
         <f t="shared" si="18"/>
         <v>p-dis-clvssrap01-osdisk</v>
       </c>
@@ -27534,10 +27518,10 @@
       <c r="Q152" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R152" s="126"/>
+      <c r="R152" s="74"/>
       <c r="S152" s="74"/>
-      <c r="T152" s="126"/>
-      <c r="U152" s="126" t="str">
+      <c r="T152" s="74"/>
+      <c r="U152" s="74" t="str">
         <f t="shared" si="19"/>
         <v>p-dis-clvssrap01-nic</v>
       </c>
@@ -27575,24 +27559,24 @@
       <c r="B153" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C153" s="126" t="str" cm="1">
+      <c r="C153" s="74" t="str" cm="1">
         <f t="array" ref="C153">UPPER(INDEX(_xlfn.TEXTSPLIT($F153, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D153" s="126" t="s">
-        <v>1117</v>
+      <c r="D153" s="74" t="s">
+        <v>1116</v>
       </c>
       <c r="E153" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F153" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G153" s="74" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="H153" s="74" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="I153" s="74">
         <v>4</v>
@@ -27612,7 +27596,7 @@
       <c r="N153" s="124" t="s">
         <v>1102</v>
       </c>
-      <c r="O153" s="127" t="str">
+      <c r="O153" s="120" t="str">
         <f t="shared" si="18"/>
         <v>p-dis-clvssrap02-osdisk</v>
       </c>
@@ -27622,18 +27606,18 @@
       <c r="Q153" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R153" s="126"/>
+      <c r="R153" s="74"/>
       <c r="S153" s="74"/>
-      <c r="T153" s="126"/>
-      <c r="U153" s="126" t="str">
+      <c r="T153" s="74"/>
+      <c r="U153" s="74" t="str">
         <f t="shared" si="19"/>
         <v>p-dis-clvssrap02-nic</v>
       </c>
-      <c r="V153" s="95" t="s">
-        <v>1106</v>
-      </c>
-      <c r="W153" s="95" t="s">
-        <v>1106</v>
+      <c r="V153" s="95" t="b">
+        <v>1</v>
+      </c>
+      <c r="W153" s="95" t="b">
+        <v>1</v>
       </c>
       <c r="X153" s="95" t="s">
         <v>317</v>
@@ -27663,24 +27647,24 @@
       <c r="B154" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C154" s="126" t="str" cm="1">
+      <c r="C154" s="74" t="str" cm="1">
         <f t="array" ref="C154">UPPER(INDEX(_xlfn.TEXTSPLIT($F154, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D154" s="126" t="s">
-        <v>1117</v>
+      <c r="D154" s="74" t="s">
+        <v>1116</v>
       </c>
       <c r="E154" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F154" s="82" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G154" s="74" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="H154" s="74" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="I154" s="74">
         <v>2</v>
@@ -27700,7 +27684,7 @@
       <c r="N154" s="124" t="s">
         <v>1102</v>
       </c>
-      <c r="O154" s="127" t="str">
+      <c r="O154" s="120" t="str">
         <f t="shared" si="18"/>
         <v>p-dis-clvadmweb01-osdisk</v>
       </c>
@@ -27710,10 +27694,10 @@
       <c r="Q154" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R154" s="126"/>
+      <c r="R154" s="74"/>
       <c r="S154" s="74"/>
-      <c r="T154" s="126"/>
-      <c r="U154" s="126" t="str">
+      <c r="T154" s="74"/>
+      <c r="U154" s="74" t="str">
         <f t="shared" si="19"/>
         <v>p-dis-clvadmweb01-nic</v>
       </c>
@@ -27751,24 +27735,24 @@
       <c r="B155" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C155" s="126" t="str" cm="1">
+      <c r="C155" s="74" t="str" cm="1">
         <f t="array" ref="C155">UPPER(INDEX(_xlfn.TEXTSPLIT($F155, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D155" s="126" t="s">
-        <v>1117</v>
+      <c r="D155" s="74" t="s">
+        <v>1116</v>
       </c>
       <c r="E155" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F155" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G155" s="74" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H155" s="74" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="I155" s="74">
         <v>2</v>
@@ -27788,7 +27772,7 @@
       <c r="N155" s="124" t="s">
         <v>1102</v>
       </c>
-      <c r="O155" s="127" t="str">
+      <c r="O155" s="120" t="str">
         <f t="shared" si="18"/>
         <v>p-dis-clvadmweb02-osdisk</v>
       </c>
@@ -27798,18 +27782,18 @@
       <c r="Q155" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R155" s="126"/>
+      <c r="R155" s="74"/>
       <c r="S155" s="74"/>
-      <c r="T155" s="126"/>
-      <c r="U155" s="126" t="str">
+      <c r="T155" s="74"/>
+      <c r="U155" s="74" t="str">
         <f t="shared" si="19"/>
         <v>p-dis-clvadmweb02-nic</v>
       </c>
-      <c r="V155" s="95" t="s">
-        <v>1106</v>
-      </c>
-      <c r="W155" s="95" t="s">
-        <v>1106</v>
+      <c r="V155" s="95" t="b">
+        <v>1</v>
+      </c>
+      <c r="W155" s="95" t="b">
+        <v>1</v>
       </c>
       <c r="X155" s="95" t="s">
         <v>317</v>
@@ -27839,24 +27823,24 @@
       <c r="B156" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C156" s="126" t="str" cm="1">
+      <c r="C156" s="74" t="str" cm="1">
         <f t="array" ref="C156">UPPER(INDEX(_xlfn.TEXTSPLIT($F156, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D156" s="126" t="s">
-        <v>1117</v>
+      <c r="D156" s="74" t="s">
+        <v>1116</v>
       </c>
       <c r="E156" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F156" s="82" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G156" s="74" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H156" s="74" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="I156" s="74">
         <v>4</v>
@@ -27876,7 +27860,7 @@
       <c r="N156" s="124" t="s">
         <v>1102</v>
       </c>
-      <c r="O156" s="127" t="str">
+      <c r="O156" s="120" t="str">
         <f t="shared" si="18"/>
         <v>p-dis-clvadmap01-osdisk</v>
       </c>
@@ -27886,10 +27870,10 @@
       <c r="Q156" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R156" s="126"/>
+      <c r="R156" s="74"/>
       <c r="S156" s="74"/>
-      <c r="T156" s="126"/>
-      <c r="U156" s="126" t="str">
+      <c r="T156" s="74"/>
+      <c r="U156" s="74" t="str">
         <f t="shared" si="19"/>
         <v>p-dis-clvadmap01-nic</v>
       </c>
@@ -27927,24 +27911,24 @@
       <c r="B157" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C157" s="128" t="str" cm="1">
+      <c r="C157" s="95" t="str" cm="1">
         <f t="array" ref="C157">UPPER(INDEX(_xlfn.TEXTSPLIT($F157, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D157" s="126" t="s">
-        <v>1117</v>
+      <c r="D157" s="74" t="s">
+        <v>1116</v>
       </c>
       <c r="E157" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F157" s="95" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G157" s="95" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="H157" s="95" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="I157" s="95">
         <v>4</v>
@@ -27964,7 +27948,7 @@
       <c r="N157" s="124" t="s">
         <v>1102</v>
       </c>
-      <c r="O157" s="129" t="str">
+      <c r="O157" s="123" t="str">
         <f t="shared" si="18"/>
         <v>p-dis-clvadmap02-osdisk</v>
       </c>
@@ -27974,18 +27958,18 @@
       <c r="Q157" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="R157" s="128"/>
+      <c r="R157" s="95"/>
       <c r="S157" s="95"/>
-      <c r="T157" s="128"/>
-      <c r="U157" s="128" t="str">
+      <c r="T157" s="95"/>
+      <c r="U157" s="95" t="str">
         <f t="shared" si="19"/>
         <v>p-dis-clvadmap02-nic</v>
       </c>
-      <c r="V157" s="95" t="s">
-        <v>1106</v>
-      </c>
-      <c r="W157" s="95" t="s">
-        <v>1106</v>
+      <c r="V157" s="95" t="b">
+        <v>1</v>
+      </c>
+      <c r="W157" s="95" t="b">
+        <v>1</v>
       </c>
       <c r="X157" s="95" t="s">
         <v>317</v>
@@ -36256,7 +36240,7 @@
         <v>SEC</v>
       </c>
       <c r="D155" s="78" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E155" s="78" t="s">
         <v>24</v>
@@ -36310,7 +36294,7 @@
         <v>SEC</v>
       </c>
       <c r="D156" s="80" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E156" s="80" t="s">
         <v>24</v>
@@ -36370,7 +36354,7 @@
         <v>24</v>
       </c>
       <c r="F157" s="82" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G157" s="73" t="str">
         <f t="shared" si="4"/>
@@ -36424,7 +36408,7 @@
         <v>24</v>
       </c>
       <c r="F158" s="74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G158" s="74" t="str">
         <f t="shared" si="4"/>
@@ -36478,7 +36462,7 @@
         <v>24</v>
       </c>
       <c r="F159" s="82" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G159" s="73" t="str">
         <f t="shared" si="4"/>
@@ -36532,7 +36516,7 @@
         <v>24</v>
       </c>
       <c r="F160" s="74" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G160" s="74" t="str">
         <f t="shared" si="4"/>
@@ -36586,7 +36570,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="82" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G161" s="73" t="str">
         <f t="shared" si="4"/>
@@ -36640,7 +36624,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="74" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G162" s="74" t="str">
         <f t="shared" si="4"/>
@@ -36694,7 +36678,7 @@
         <v>24</v>
       </c>
       <c r="F163" s="82" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G163" s="73" t="str">
         <f t="shared" si="4"/>
@@ -36748,7 +36732,7 @@
         <v>24</v>
       </c>
       <c r="F164" s="74" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G164" s="74" t="str">
         <f t="shared" si="4"/>
@@ -36802,7 +36786,7 @@
         <v>24</v>
       </c>
       <c r="F165" s="82" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G165" s="73" t="str">
         <f t="shared" si="4"/>
@@ -36856,7 +36840,7 @@
         <v>24</v>
       </c>
       <c r="F166" s="118" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G166" s="74" t="str">
         <f t="shared" si="4"/>
@@ -43283,7 +43267,7 @@
         <v>317</v>
       </c>
       <c r="G163" s="118" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="H163" s="118" t="s">
         <v>965</v>
@@ -43331,7 +43315,7 @@
         <v>1103</v>
       </c>
       <c r="J164" s="117" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="K164" s="117" t="str">
         <f t="shared" si="9"/>
@@ -43370,7 +43354,7 @@
         <v>1104</v>
       </c>
       <c r="J165" s="118" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="K165" s="118" t="str">
         <f t="shared" si="9"/>
@@ -43406,7 +43390,7 @@
         <v>340</v>
       </c>
       <c r="I166" s="117" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="J166" s="117" t="s">
         <v>922</v>
@@ -43445,7 +43429,7 @@
         <v>340</v>
       </c>
       <c r="I167" s="118" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="J167" s="118" t="s">
         <v>922</v>
@@ -43484,7 +43468,7 @@
         <v>340</v>
       </c>
       <c r="I168" s="117" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="J168" s="117" t="s">
         <v>922</v>
@@ -43523,7 +43507,7 @@
         <v>340</v>
       </c>
       <c r="I169" s="118" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J169" s="118" t="s">
         <v>922</v>
@@ -43562,7 +43546,7 @@
         <v>340</v>
       </c>
       <c r="I170" s="117" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="J170" s="117" t="s">
         <v>922</v>
@@ -43601,7 +43585,7 @@
         <v>340</v>
       </c>
       <c r="I171" s="118" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="J171" s="118" t="s">
         <v>922</v>
@@ -43640,7 +43624,7 @@
         <v>340</v>
       </c>
       <c r="I172" s="117" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="J172" s="117" t="s">
         <v>922</v>
@@ -43679,7 +43663,7 @@
         <v>340</v>
       </c>
       <c r="I173" s="118" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="J173" s="118" t="s">
         <v>922</v>
@@ -43718,7 +43702,7 @@
         <v>340</v>
       </c>
       <c r="I174" s="117" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="J174" s="117" t="s">
         <v>922</v>
@@ -43757,7 +43741,7 @@
         <v>340</v>
       </c>
       <c r="I175" s="118" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="J175" s="118" t="s">
         <v>922</v>
@@ -48626,7 +48610,7 @@
         <v>24</v>
       </c>
       <c r="F45" s="74" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G45" s="74" t="s">
         <v>111</v>
@@ -48645,19 +48629,19 @@
         <v>p-sec-mevrsol-lb-fe</v>
       </c>
       <c r="L45" s="74" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="M45" s="74" t="s">
+        <v>1106</v>
+      </c>
+      <c r="N45" s="74" t="s">
         <v>1107</v>
-      </c>
-      <c r="N45" s="74" t="s">
-        <v>1108</v>
       </c>
       <c r="O45" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P45" s="74" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="Q45" s="74" t="str">
         <f t="shared" si="6"/>
@@ -48666,25 +48650,25 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B46" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C46" s="82" t="str" cm="1">
         <f t="array" ref="C46">UPPER(INDEX(_xlfn.TEXTSPLIT($F46, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D46" s="82" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E46" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F46" s="82" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G46" s="82"/>
       <c r="H46" s="82"/>
       <c r="I46" s="82" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="J46" s="82" t="s">
         <v>102</v>
@@ -48694,19 +48678,19 @@
         <v>p-dis-clvweb-lb-fe</v>
       </c>
       <c r="L46" s="82" t="s">
+        <v>1132</v>
+      </c>
+      <c r="M46" s="82" t="s">
         <v>1133</v>
       </c>
-      <c r="M46" s="82" t="s">
-        <v>1134</v>
-      </c>
       <c r="N46" s="82" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="O46" s="82" t="s">
         <v>108</v>
       </c>
       <c r="P46" s="82" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="Q46" s="82" t="str">
         <f t="shared" si="6"/>
@@ -48715,25 +48699,25 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B47" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C47" s="74" t="str" cm="1">
         <f t="array" ref="C47">UPPER(INDEX(_xlfn.TEXTSPLIT($F47, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D47" s="74" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E47" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F47" s="74" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G47" s="74"/>
       <c r="H47" s="74"/>
       <c r="I47" s="74" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="J47" s="74" t="s">
         <v>102</v>
@@ -48746,16 +48730,16 @@
         <v>317</v>
       </c>
       <c r="M47" s="74" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="N47" s="74" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="O47" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P47" s="74" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="Q47" s="74" t="str">
         <f t="shared" si="6"/>
@@ -48764,25 +48748,25 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C48" s="82" t="str" cm="1">
         <f t="array" ref="C48">UPPER(INDEX(_xlfn.TEXTSPLIT($F48, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D48" s="82" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E48" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F48" s="82" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G48" s="82"/>
       <c r="H48" s="82"/>
       <c r="I48" s="82" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="J48" s="82" t="s">
         <v>102</v>
@@ -48792,10 +48776,10 @@
         <v>p-dis-clvssrap-lb-fe</v>
       </c>
       <c r="L48" s="82" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="M48" s="82" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="N48" s="82" t="s">
         <v>340</v>
@@ -48804,7 +48788,7 @@
         <v>108</v>
       </c>
       <c r="P48" s="82" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="Q48" s="82" t="str">
         <f t="shared" si="6"/>
@@ -48813,25 +48797,25 @@
     </row>
     <row r="49" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B49" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C49" s="74" t="str" cm="1">
         <f t="array" ref="C49">UPPER(INDEX(_xlfn.TEXTSPLIT($F49, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D49" s="74" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E49" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F49" s="74" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G49" s="74"/>
       <c r="H49" s="74"/>
       <c r="I49" s="74" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="J49" s="74" t="s">
         <v>102</v>
@@ -48844,16 +48828,16 @@
         <v>317</v>
       </c>
       <c r="M49" s="74" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="N49" s="74" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="O49" s="74" t="s">
         <v>108</v>
       </c>
       <c r="P49" s="74" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="Q49" s="74" t="str">
         <f t="shared" si="6"/>
@@ -48862,25 +48846,25 @@
     </row>
     <row r="50" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B50" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C50" s="82" t="str" cm="1">
         <f t="array" ref="C50">UPPER(INDEX(_xlfn.TEXTSPLIT($F50, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D50" s="82" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E50" s="82" t="s">
         <v>24</v>
       </c>
       <c r="F50" s="82" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G50" s="82"/>
       <c r="H50" s="82"/>
       <c r="I50" s="82" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="J50" s="82" t="s">
         <v>102</v>
@@ -48890,10 +48874,10 @@
         <v>p-dis-clvadmap-lb-fe</v>
       </c>
       <c r="L50" s="82" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="M50" s="82" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="N50" s="82" t="s">
         <v>340</v>
@@ -48902,7 +48886,7 @@
         <v>108</v>
       </c>
       <c r="P50" s="82" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="Q50" s="82" t="str">
         <f t="shared" si="6"/>
@@ -51103,10 +51087,10 @@
         <v>SEC</v>
       </c>
       <c r="D67" s="74" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E67" s="74" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F67" s="74" t="str">
         <f t="shared" si="15"/>
@@ -51136,10 +51120,10 @@
         <v>SEC</v>
       </c>
       <c r="D68" s="74" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E68" s="74" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F68" s="74" t="str">
         <f t="shared" si="15"/>
@@ -51169,10 +51153,10 @@
         <v>SEC</v>
       </c>
       <c r="D69" s="74" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E69" s="74" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F69" s="74" t="str">
         <f t="shared" si="15"/>
@@ -51202,10 +51186,10 @@
         <v>SEC</v>
       </c>
       <c r="D70" s="74" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E70" s="74" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F70" s="74" t="str">
         <f t="shared" si="15"/>
@@ -51235,10 +51219,10 @@
         <v>SEC</v>
       </c>
       <c r="D71" s="74" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E71" s="74" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F71" s="74" t="str">
         <f t="shared" si="15"/>
@@ -51268,10 +51252,10 @@
         <v>SEC</v>
       </c>
       <c r="D72" s="74" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="E72" s="74" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F72" s="74" t="str">
         <f t="shared" si="15"/>
@@ -51293,24 +51277,24 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B73" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C73" s="82" t="str" cm="1">
         <f t="array" ref="C73">UPPER(INDEX(_xlfn.TEXTSPLIT($D73, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D73" s="82" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E73" s="82" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="F73" s="82" t="str">
         <f t="shared" si="15"/>
         <v>p-dis-clvweb-lb-pb443</v>
       </c>
       <c r="G73" s="82" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H73" s="82">
         <v>443</v>
@@ -51325,24 +51309,24 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B74" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C74" s="82" t="str" cm="1">
         <f t="array" ref="C74">UPPER(INDEX(_xlfn.TEXTSPLIT($D74, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D74" s="74" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E74" s="74" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="F74" s="74" t="str">
         <f t="shared" si="15"/>
         <v>p-dis-clvap-lb-pb8080</v>
       </c>
       <c r="G74" s="74" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H74" s="74">
         <v>8080</v>
@@ -51357,24 +51341,24 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B75" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C75" s="82" t="str" cm="1">
         <f t="array" ref="C75">UPPER(INDEX(_xlfn.TEXTSPLIT($D75, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D75" s="82" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E75" s="82" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="F75" s="82" t="str">
         <f t="shared" si="15"/>
         <v>p-dis-clvssrap-lb-pb8080</v>
       </c>
       <c r="G75" s="82" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H75" s="82">
         <v>8080</v>
@@ -51389,24 +51373,24 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B76" s="74" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C76" s="82" t="str" cm="1">
         <f t="array" ref="C76">UPPER(INDEX(_xlfn.TEXTSPLIT($D76, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D76" s="74" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E76" s="74" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F76" s="74" t="str">
         <f t="shared" si="15"/>
         <v>p-dis-clvadmweb-lb-pb443</v>
       </c>
       <c r="G76" s="74" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H76" s="74">
         <v>443</v>
@@ -51421,24 +51405,24 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B77" s="82" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C77" s="82" t="str" cm="1">
         <f t="array" ref="C77">UPPER(INDEX(_xlfn.TEXTSPLIT($D77, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D77" s="82" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E77" s="82" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="F77" s="82" t="str">
         <f t="shared" si="15"/>
         <v>p-dis-clvadmap-lb-pb8080</v>
       </c>
       <c r="G77" s="82" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H77" s="82">
         <v>8080</v>
@@ -51458,21 +51442,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -51616,10 +51585,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -51641,19 +51635,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/서버정보/20260911_리소스배포_운영.xlsx
+++ b/서버정보/20260911_리소스배포_운영.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CC1701-44BB-42BA-A4DD-F198171B1669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2BA3CA-79F9-4086-9E22-6DD45D2021E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51442,6 +51442,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -51585,35 +51600,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -51635,9 +51625,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>